--- a/artfynd/A 44655-2023 artfynd.xlsx
+++ b/artfynd/A 44655-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -801,6 +801,226 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>123428440</v>
+      </c>
+      <c r="B3" t="n">
+        <v>58341</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Grums-Lång, Vrm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>389118</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6591781</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Grums</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Grums</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-06-20</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-06-20</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Mikael Andersson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Mikael Andersson, Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>NVI Grums-Lång</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>123428546</v>
+      </c>
+      <c r="B4" t="n">
+        <v>5282</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>102147</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Spindelbock</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Aegomorphus clavipes</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Schrank, 1781)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Grums-Lång, Vrm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>389064</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6591750</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Grums</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Grums</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-06-20</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-06-20</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Mikael Andersson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Mikael Andersson, Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>NVI Grums-Lång</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 44655-2023 artfynd.xlsx
+++ b/artfynd/A 44655-2023 artfynd.xlsx
@@ -1013,7 +1013,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Mikael Andersson, Per Karlsson Linderum</t>
+          <t>Per Karlsson Linderum, Mikael Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">

--- a/artfynd/A 44655-2023 artfynd.xlsx
+++ b/artfynd/A 44655-2023 artfynd.xlsx
@@ -804,10 +804,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123428546</v>
+        <v>123428440</v>
       </c>
       <c r="B3" t="n">
-        <v>5282</v>
+        <v>58347</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -820,21 +820,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102147</v>
+        <v>208249</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spindelbock</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Aegomorphus clavipes</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schrank, 1781)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -848,10 +848,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>389064</v>
+        <v>389118</v>
       </c>
       <c r="R3" t="n">
-        <v>6591750</v>
+        <v>6591781</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -914,10 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123428440</v>
+        <v>123428546</v>
       </c>
       <c r="B4" t="n">
-        <v>58341</v>
+        <v>5283</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -930,21 +930,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>208249</v>
+        <v>102147</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Spindelbock</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Aegomorphus clavipes</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schrank, 1781)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -958,10 +958,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>389118</v>
+        <v>389064</v>
       </c>
       <c r="R4" t="n">
-        <v>6591781</v>
+        <v>6591750</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 44655-2023 artfynd.xlsx
+++ b/artfynd/A 44655-2023 artfynd.xlsx
@@ -807,7 +807,7 @@
         <v>123428440</v>
       </c>
       <c r="B3" t="n">
-        <v>58347</v>
+        <v>58350</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>123428546</v>
       </c>
       <c r="B4" t="n">
-        <v>5283</v>
+        <v>5285</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 44655-2023 artfynd.xlsx
+++ b/artfynd/A 44655-2023 artfynd.xlsx
@@ -804,10 +804,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123428440</v>
+        <v>123428546</v>
       </c>
       <c r="B3" t="n">
-        <v>58350</v>
+        <v>5285</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -820,21 +820,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208249</v>
+        <v>102147</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Spindelbock</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Aegomorphus clavipes</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schrank, 1781)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -848,10 +848,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>389118</v>
+        <v>389064</v>
       </c>
       <c r="R3" t="n">
-        <v>6591781</v>
+        <v>6591750</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -914,10 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123428546</v>
+        <v>123428440</v>
       </c>
       <c r="B4" t="n">
-        <v>5285</v>
+        <v>58351</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -930,21 +930,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102147</v>
+        <v>208249</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spindelbock</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Aegomorphus clavipes</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schrank, 1781)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -958,10 +958,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>389064</v>
+        <v>389118</v>
       </c>
       <c r="R4" t="n">
-        <v>6591750</v>
+        <v>6591781</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 44655-2023 artfynd.xlsx
+++ b/artfynd/A 44655-2023 artfynd.xlsx
@@ -804,10 +804,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123428546</v>
+        <v>123428440</v>
       </c>
       <c r="B3" t="n">
-        <v>5285</v>
+        <v>58351</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -820,21 +820,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102147</v>
+        <v>208249</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spindelbock</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Aegomorphus clavipes</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schrank, 1781)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -848,10 +848,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>389064</v>
+        <v>389118</v>
       </c>
       <c r="R3" t="n">
-        <v>6591750</v>
+        <v>6591781</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -914,10 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123428440</v>
+        <v>123428546</v>
       </c>
       <c r="B4" t="n">
-        <v>58351</v>
+        <v>5285</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -930,21 +930,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>208249</v>
+        <v>102147</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Spindelbock</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Aegomorphus clavipes</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schrank, 1781)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -958,10 +958,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>389118</v>
+        <v>389064</v>
       </c>
       <c r="R4" t="n">
-        <v>6591781</v>
+        <v>6591750</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 44655-2023 artfynd.xlsx
+++ b/artfynd/A 44655-2023 artfynd.xlsx
@@ -804,10 +804,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123428440</v>
+        <v>123428546</v>
       </c>
       <c r="B3" t="n">
-        <v>58351</v>
+        <v>5285</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -820,21 +820,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208249</v>
+        <v>102147</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Spindelbock</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Aegomorphus clavipes</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schrank, 1781)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -848,10 +848,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>389118</v>
+        <v>389064</v>
       </c>
       <c r="R3" t="n">
-        <v>6591781</v>
+        <v>6591750</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -914,10 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123428546</v>
+        <v>123428440</v>
       </c>
       <c r="B4" t="n">
-        <v>5285</v>
+        <v>58351</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -930,21 +930,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102147</v>
+        <v>208249</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spindelbock</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Aegomorphus clavipes</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schrank, 1781)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -958,10 +958,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>389064</v>
+        <v>389118</v>
       </c>
       <c r="R4" t="n">
-        <v>6591750</v>
+        <v>6591781</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
